--- a/artfynd/A 2447-2023 artfynd.xlsx
+++ b/artfynd/A 2447-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121139067</v>
       </c>
       <c r="B2" t="n">
-        <v>39842</v>
+        <v>39845</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 2447-2023 artfynd.xlsx
+++ b/artfynd/A 2447-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -790,6 +790,132 @@
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>125441699</v>
+      </c>
+      <c r="B3" t="n">
+        <v>58373</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>208249</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Vanlig groda</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Rana temporaria</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>vilande</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Timmerhedsslätt, Timmerhedsslätt, Vg</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>334595</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6403445</v>
+      </c>
+      <c r="S3" t="n">
+        <v>50</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Lerum</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Lerum</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-05-26</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>22:11</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-05-26</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>22:11</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Bäck</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Karin  Flodin</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Karin  Flodin</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 2447-2023 artfynd.xlsx
+++ b/artfynd/A 2447-2023 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>125441699</v>
       </c>
       <c r="B3" t="n">
-        <v>58373</v>
+        <v>58487</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 2447-2023 artfynd.xlsx
+++ b/artfynd/A 2447-2023 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>125441699</v>
       </c>
       <c r="B3" t="n">
-        <v>58507</v>
+        <v>58508</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 2447-2023 artfynd.xlsx
+++ b/artfynd/A 2447-2023 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>125441699</v>
       </c>
       <c r="B3" t="n">
-        <v>58508</v>
+        <v>58509</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 2447-2023 artfynd.xlsx
+++ b/artfynd/A 2447-2023 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121139067</v>
+        <v>125441699</v>
       </c>
       <c r="B2" t="n">
-        <v>39845</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58817</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,46 +686,46 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>214803</v>
+        <v>208249</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dolkstekelsglasvinge</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Synanthedon scoliaeformis</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Borkhausen, 1789)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
+          <t>vilande</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Lerum, Vg</t>
+          <t>Timmerhedsslätt, Timmerhedsslätt, Vg</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>334682</v>
+        <v>334595</v>
       </c>
       <c r="R2" t="n">
-        <v>6403471</v>
+        <v>6403445</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -754,17 +749,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2025-05-26</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>22:11</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>kläckhål på björk</t>
+          <t>2025-05-26</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>22:11</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -773,29 +773,33 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>Bäck</t>
+        </is>
+      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Per Karlsson Linderum</t>
+          <t>Karin  Flodin</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Per Karlsson Linderum</t>
+          <t>Karin  Flodin</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125441699</v>
+        <v>121139067</v>
       </c>
       <c r="B3" t="n">
-        <v>58509</v>
+        <v>40300</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,46 +807,46 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>208249</v>
+        <v>214803</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Dolkstekelsglasvinge</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Synanthedon scoliaeformis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Borkhausen, 1789)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>vilande</t>
-        </is>
-      </c>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Timmerhedsslätt, Timmerhedsslätt, Vg</t>
+          <t>Lerum, Vg</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>334595</v>
+        <v>334682</v>
       </c>
       <c r="R3" t="n">
-        <v>6403445</v>
+        <v>6403471</v>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -866,22 +870,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>22:11</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>22:11</t>
+          <t>2024-08-28</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>kläckhål på björk</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -890,23 +889,19 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Bäck</t>
-        </is>
-      </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Karin  Flodin</t>
+          <t>Per Karlsson Linderum</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Karin  Flodin</t>
+          <t>Per Karlsson Linderum</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>

--- a/artfynd/A 2447-2023 artfynd.xlsx
+++ b/artfynd/A 2447-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -793,6 +798,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125441699</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -905,8 +915,17 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121139067</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>